--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>227</v>
+        <v>408</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>338</v>
+        <v>393</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E3">
         <v>0</v>
